--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-24).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-24).xlsx
@@ -912,48 +912,48 @@
   </si>
   <si>
     <t>214
-183</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>R$ 583.797,30</t>
-  </si>
-  <si>
-    <t>R$ 2.993,83
-R$ 3.063,57</t>
+185</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>R$ 586.498,74</t>
+  </si>
+  <si>
+    <t>R$ 2.977,15
+R$ 3.045,05</t>
   </si>
   <si>
     <t>0.5%
 2.8%</t>
   </si>
   <si>
-    <t>33.9</t>
+    <t>33.7</t>
   </si>
   <si>
     <t>(3.8%)</t>
   </si>
   <si>
-    <t>(163.5%)</t>
-  </si>
-  <si>
-    <t>(200.9%)</t>
-  </si>
-  <si>
-    <t>4.6%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>25.5</t>
+    <t>(162.7%)</t>
+  </si>
+  <si>
+    <t>(200.0%)</t>
+  </si>
+  <si>
+    <t>4.7%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>25.6</t>
   </si>
   <si>
     <t>76.7%</t>
   </si>
   <si>
-    <t>7.6%</t>
+    <t>7.7%</t>
   </si>
   <si>
     <t>4.6</t>
@@ -968,13 +968,13 @@
     <t>17.7</t>
   </si>
   <si>
-    <t>77.2%</t>
+    <t>77.1%</t>
   </si>
   <si>
     <t>-R$ 13.815,49</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5994,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6030,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>2178</v>
+      </c>
+      <c r="P36" s="5">
+        <v>2178</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.33415007656967832</v>
+      </c>
+      <c r="R36" s="7">
+        <v>29</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.35060013774104681</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.023589118457300273</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.23944949494949494</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.15168549127640035</v>
+      </c>
+      <c r="X36" s="8">
+        <v>37.670588235294119</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.5488107142857146</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>8.5212090909090907</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>16.182976</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>18.469605882352941</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.52941176470588236</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7915,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7951,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>523.44000000000005</v>
+      </c>
+      <c r="P51" s="5">
+        <v>523.44000000000005</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.56744070737955532</v>
+      </c>
+      <c r="R51" s="7">
+        <v>5</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.66666666666666674</v>
+      </c>
+      <c r="T51" s="6">
+        <v>-0.088720770288858303</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.42148097203117835</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.051702200825309484</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.19285304906006417</v>
+      </c>
+      <c r="X51" s="8">
+        <v>71.783349999999999</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>2.61334</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>57.375</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>59.5</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12660,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -16163,7 +16235,7 @@
         <v>0.008320732665552966</v>
       </c>
       <c r="W116" s="6">
-        <v>-0.021805318032050814</v>
+        <v>0.008320732665552966</v>
       </c>
       <c r="X116" s="8">
         <v>30.51573888888889</v>
@@ -16845,7 +16917,7 @@
         <v>-146.59999999999999</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17107,7 +17179,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17500,7 +17572,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18677,7 +18749,7 @@
         <v>-289.30000000000001</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18808,7 +18880,7 @@
         <v>-230.5</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20991,7 +21063,7 @@
         <v>-51.899999999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21118,7 +21190,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22271,7 +22343,7 @@
         <v>-11.83</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28436,7 +28508,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
